--- a/Excel/PetAtrConfig.xlsx
+++ b/Excel/PetAtrConfig.xlsx
@@ -30,7 +30,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
-    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0">
@@ -56,34 +55,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-实际生效值/10</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="37">
   <si>
     <t>#</t>
   </si>
@@ -97,19 +74,16 @@
     <t>Role</t>
   </si>
   <si>
-    <t>AttrId</t>
-  </si>
-  <si>
-    <t>MinValue</t>
-  </si>
-  <si>
-    <t>MaxValue</t>
-  </si>
-  <si>
-    <t>QualitRise</t>
-  </si>
-  <si>
-    <t>Percent</t>
+    <t>AtrId</t>
+  </si>
+  <si>
+    <t>AtrVue</t>
+  </si>
+  <si>
+    <t>FlairMin</t>
+  </si>
+  <si>
+    <t>FlairMax</t>
   </si>
   <si>
     <t>StartQuality</t>
@@ -142,7 +116,7 @@
     <t>杀敌生命</t>
   </si>
   <si>
-    <t>十敌防御</t>
+    <t>杀敌防御</t>
   </si>
   <si>
     <t>杀敌物攻</t>
@@ -1165,32 +1139,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="5" width="12.8333333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="17.125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="14.0833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="13" width="13" style="1" customWidth="1"/>
-    <col min="14" max="14" width="17" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:14">
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:14">
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" customHeight="1" spans="1:13">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:13">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1224,13 +1198,10 @@
       <c r="M3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="2" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C4" s="2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C4" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1260,126 +1231,114 @@
         <v>10</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1">
-        <v>9</v>
-      </c>
-      <c r="M6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="I7" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1">
-        <v>9</v>
-      </c>
-      <c r="M7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -1388,33 +1347,30 @@
         <v>2</v>
       </c>
       <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>10</v>
+      </c>
+      <c r="I8" s="1">
+        <v>100</v>
+      </c>
+      <c r="J8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="1">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>100</v>
-      </c>
       <c r="K8" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1">
-        <v>9</v>
-      </c>
-      <c r="M8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -1423,33 +1379,30 @@
         <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1">
-        <v>9</v>
-      </c>
-      <c r="M9" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -1458,33 +1411,30 @@
         <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1">
-        <v>9</v>
-      </c>
-      <c r="M10" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -1493,28 +1443,25 @@
         <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1">
-        <v>9</v>
-      </c>
-      <c r="M11" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1525,22 +1472,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
       </c>
       <c r="J12" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K12" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1">
-        <v>9</v>
-      </c>
-      <c r="M12" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1551,48 +1498,48 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1">
+        <v>6</v>
+      </c>
+      <c r="K13" s="1">
+        <v>9</v>
+      </c>
+      <c r="L13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:13">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="1">
-        <v>10</v>
-      </c>
-      <c r="K13" s="1">
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="J14" s="1">
         <v>6</v>
       </c>
-      <c r="L13" s="1">
-        <v>9</v>
-      </c>
-      <c r="M13" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:14">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="1">
-        <v>10</v>
-      </c>
       <c r="K14" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L14" s="1">
-        <v>9</v>
-      </c>
-      <c r="M14" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1603,22 +1550,22 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
       </c>
       <c r="J15" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K15" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L15" s="1">
-        <v>9</v>
-      </c>
-      <c r="M15" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1629,22 +1576,22 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
       </c>
       <c r="J16" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K16" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L16" s="1">
-        <v>9</v>
-      </c>
-      <c r="M16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1655,22 +1602,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
       </c>
       <c r="J17" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="K17" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L17" s="1">
-        <v>9</v>
-      </c>
-      <c r="M17" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1681,22 +1628,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
       </c>
       <c r="J18" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="K18" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L18" s="1">
-        <v>9</v>
-      </c>
-      <c r="M18" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1707,22 +1654,22 @@
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
       </c>
       <c r="J19" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="K19" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L19" s="1">
-        <v>9</v>
-      </c>
-      <c r="M19" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1733,22 +1680,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2</v>
       </c>
       <c r="J20" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="K20" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L20" s="1">
-        <v>9</v>
-      </c>
-      <c r="M20" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -1759,22 +1706,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
       </c>
       <c r="J21" s="1">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="K21" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L21" s="1">
-        <v>9</v>
-      </c>
-      <c r="M21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -1785,22 +1732,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2</v>
       </c>
       <c r="J22" s="1">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="K22" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L22" s="1">
-        <v>9</v>
-      </c>
-      <c r="M22" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1811,22 +1758,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2</v>
       </c>
       <c r="J23" s="1">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="K23" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L23" s="1">
-        <v>9</v>
-      </c>
-      <c r="M23" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -1837,22 +1784,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2</v>
       </c>
       <c r="J24" s="1">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="K24" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L24" s="1">
-        <v>9</v>
-      </c>
-      <c r="M24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1863,22 +1810,22 @@
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2</v>
       </c>
       <c r="J25" s="1">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="K25" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L25" s="1">
-        <v>9</v>
-      </c>
-      <c r="M25" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -1889,24 +1836,24 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
       </c>
       <c r="J26" s="1">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="K26" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L26" s="1">
-        <v>9</v>
-      </c>
-      <c r="M26" s="1">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PetAtrConfig.xlsx
+++ b/Excel/PetAtrConfig.xlsx
@@ -349,12 +349,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1298,7 +1298,7 @@
         <v>9</v>
       </c>
       <c r="L6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
       <c r="L7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1362,7 +1362,7 @@
         <v>9</v>
       </c>
       <c r="L8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1394,7 +1394,7 @@
         <v>9</v>
       </c>
       <c r="L9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1426,7 +1426,7 @@
         <v>9</v>
       </c>
       <c r="L10" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -1458,7 +1458,7 @@
         <v>9</v>
       </c>
       <c r="L11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">

--- a/Excel/PetAtrConfig.xlsx
+++ b/Excel/PetAtrConfig.xlsx
@@ -349,12 +349,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1283,10 +1283,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H6" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I6" s="1">
         <v>100</v>
@@ -1315,13 +1315,13 @@
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I7" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
@@ -1347,10 +1347,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I8" s="1">
         <v>100</v>
@@ -1379,10 +1379,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I9" s="1">
         <v>50</v>
@@ -1411,10 +1411,10 @@
         <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I10" s="1">
         <v>50</v>
@@ -1443,10 +1443,10 @@
         <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I11" s="1">
         <v>50</v>

--- a/Excel/PetAtrConfig.xlsx
+++ b/Excel/PetAtrConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -71,6 +71,12 @@
     <t>Name</t>
   </si>
   <si>
+    <t>StartId</t>
+  </si>
+  <si>
+    <t>EndId</t>
+  </si>
+  <si>
     <t>Role</t>
   </si>
   <si>
@@ -126,42 +132,6 @@
   </si>
   <si>
     <t>杀敌道攻</t>
-  </si>
-  <si>
-    <t>十敌加攻</t>
-  </si>
-  <si>
-    <t>十敌加血</t>
-  </si>
-  <si>
-    <t>十敌加防</t>
-  </si>
-  <si>
-    <t>百敌加攻</t>
-  </si>
-  <si>
-    <t>百敌加血</t>
-  </si>
-  <si>
-    <t>百敌加防</t>
-  </si>
-  <si>
-    <t>千敌加攻</t>
-  </si>
-  <si>
-    <t>千敌加血</t>
-  </si>
-  <si>
-    <t>千敌加防</t>
-  </si>
-  <si>
-    <t>万敌攻加</t>
-  </si>
-  <si>
-    <t>万敌血加</t>
-  </si>
-  <si>
-    <t>万敌防加</t>
   </si>
   <si>
     <t>万敌攻增</t>
@@ -360,7 +330,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,7 +339,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,7 +672,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -714,16 +696,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -732,94 +714,96 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1139,641 +1123,839 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="12.8333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.0833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="4" max="7" width="12.8333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
+    <col min="13" max="14" width="13" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:13">
-      <c r="M1" s="1" t="s">
+    <row r="1" customHeight="1" spans="3:15">
+      <c r="O1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:13">
-      <c r="M2" s="1" t="s">
+    <row r="2" customHeight="1" spans="3:15">
+      <c r="O2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="C4" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="O3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <v>20</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>50</v>
       </c>
-      <c r="I6" s="1">
+      <c r="K6" s="1">
         <v>100</v>
       </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
         <v>9</v>
       </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>3</v>
       </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
         <v>50</v>
       </c>
-      <c r="I7" s="1">
+      <c r="K7" s="1">
         <v>100</v>
       </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
         <v>9</v>
       </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>2</v>
       </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
         <v>50</v>
       </c>
-      <c r="I8" s="1">
+      <c r="K8" s="1">
         <v>100</v>
       </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
         <v>9</v>
       </c>
-      <c r="L8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
         <v>4</v>
       </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
         <v>25</v>
       </c>
-      <c r="I9" s="1">
+      <c r="K9" s="1">
         <v>50</v>
       </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
         <v>9</v>
       </c>
-      <c r="L9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>24</v>
+      </c>
+      <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="H10" s="1">
         <v>5</v>
       </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
         <v>25</v>
       </c>
-      <c r="I10" s="1">
+      <c r="K10" s="1">
         <v>50</v>
       </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
         <v>9</v>
       </c>
-      <c r="L10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="C11" s="1">
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C11" s="2">
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>24</v>
+      </c>
+      <c r="G11" s="2">
         <v>3</v>
       </c>
-      <c r="F11" s="1">
+      <c r="H11" s="2">
         <v>6</v>
       </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
         <v>25</v>
       </c>
-      <c r="I11" s="1">
+      <c r="K11" s="2">
         <v>50</v>
       </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2">
         <v>9</v>
       </c>
-      <c r="L11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="N11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="E12" s="1">
+        <v>25</v>
+      </c>
+      <c r="F12" s="1">
+        <v>48</v>
       </c>
       <c r="G12" s="1">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>20</v>
       </c>
       <c r="J12" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K12" s="1">
+        <v>80</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
         <v>9</v>
       </c>
-      <c r="L12" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="E13" s="1">
+        <v>25</v>
+      </c>
+      <c r="F13" s="1">
+        <v>48</v>
       </c>
       <c r="G13" s="1">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
       </c>
       <c r="J13" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K13" s="1">
+        <v>80</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
         <v>9</v>
       </c>
-      <c r="L13" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:13">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:15">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="E14" s="1">
+        <v>25</v>
+      </c>
+      <c r="F14" s="1">
+        <v>48</v>
       </c>
       <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>2</v>
       </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
       <c r="J14" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K14" s="1">
+        <v>80</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
         <v>9</v>
       </c>
-      <c r="L14" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1">
         <v>25</v>
       </c>
+      <c r="F15" s="1">
+        <v>48</v>
+      </c>
       <c r="G15" s="1">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
       </c>
       <c r="J15" s="1">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K15" s="1">
+        <v>40</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
         <v>9</v>
       </c>
-      <c r="L15" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="N15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="E16" s="1">
+        <v>25</v>
+      </c>
+      <c r="F16" s="1">
+        <v>48</v>
       </c>
       <c r="G16" s="1">
         <v>2</v>
       </c>
+      <c r="H16" s="1">
+        <v>5</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
       <c r="J16" s="1">
+        <v>20</v>
+      </c>
+      <c r="K16" s="1">
+        <v>40</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
+        <v>9</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="2">
+        <v>25</v>
+      </c>
+      <c r="F17" s="2">
+        <v>48</v>
+      </c>
+      <c r="G17" s="2">
+        <v>3</v>
+      </c>
+      <c r="H17" s="2">
         <v>6</v>
       </c>
-      <c r="K16" s="1">
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
+        <v>20</v>
+      </c>
+      <c r="K17" s="4">
+        <v>40</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1</v>
+      </c>
+      <c r="M17" s="2">
         <v>9</v>
       </c>
-      <c r="L16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="1">
-        <v>2</v>
-      </c>
-      <c r="J17" s="1">
-        <v>6</v>
-      </c>
-      <c r="K17" s="1">
-        <v>9</v>
-      </c>
-      <c r="L17" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="N17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="E18" s="1">
+        <v>49</v>
+      </c>
+      <c r="F18" s="1">
+        <v>72</v>
       </c>
       <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>20</v>
+      </c>
+      <c r="J18" s="1">
+        <v>30</v>
+      </c>
+      <c r="K18" s="1">
+        <v>60</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
+        <v>9</v>
+      </c>
+      <c r="N18" s="1">
         <v>2</v>
       </c>
-      <c r="J18" s="1">
-        <v>6</v>
-      </c>
-      <c r="K18" s="1">
-        <v>9</v>
-      </c>
-      <c r="L18" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
+      </c>
+      <c r="E19" s="1">
+        <v>49</v>
+      </c>
+      <c r="F19" s="1">
+        <v>72</v>
       </c>
       <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>3</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1">
+        <v>30</v>
+      </c>
+      <c r="K19" s="1">
+        <v>60</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
+        <v>9</v>
+      </c>
+      <c r="N19" s="1">
         <v>2</v>
       </c>
-      <c r="J19" s="1">
-        <v>6</v>
-      </c>
-      <c r="K19" s="1">
-        <v>9</v>
-      </c>
-      <c r="L19" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="1">
+        <v>49</v>
+      </c>
+      <c r="F20" s="1">
+        <v>72</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
         <v>30</v>
       </c>
-      <c r="G20" s="1">
+      <c r="K20" s="1">
+        <v>60</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1">
+        <v>9</v>
+      </c>
+      <c r="N20" s="1">
         <v>2</v>
       </c>
-      <c r="J20" s="1">
-        <v>6</v>
-      </c>
-      <c r="K20" s="1">
-        <v>9</v>
-      </c>
-      <c r="L20" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="E21" s="1">
+        <v>49</v>
+      </c>
+      <c r="F21" s="1">
+        <v>72</v>
       </c>
       <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>15</v>
+      </c>
+      <c r="K21" s="1">
+        <v>30</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
+        <v>9</v>
+      </c>
+      <c r="N21" s="1">
         <v>2</v>
       </c>
-      <c r="J21" s="1">
-        <v>6</v>
-      </c>
-      <c r="K21" s="1">
-        <v>9</v>
-      </c>
-      <c r="L21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
+      </c>
+      <c r="E22" s="1">
+        <v>49</v>
+      </c>
+      <c r="F22" s="1">
+        <v>72</v>
       </c>
       <c r="G22" s="1">
         <v>2</v>
       </c>
+      <c r="H22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
       <c r="J22" s="1">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K22" s="1">
+        <v>30</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1">
         <v>9</v>
       </c>
-      <c r="L22" s="1">
+      <c r="N22" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
+      </c>
+      <c r="E23" s="1">
+        <v>49</v>
+      </c>
+      <c r="F23" s="1">
+        <v>72</v>
       </c>
       <c r="G23" s="1">
+        <v>3</v>
+      </c>
+      <c r="H23" s="1">
+        <v>6</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>15</v>
+      </c>
+      <c r="K23" s="1">
+        <v>30</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1">
+        <v>9</v>
+      </c>
+      <c r="N23" s="1">
         <v>2</v>
       </c>
-      <c r="J23" s="1">
-        <v>6</v>
-      </c>
-      <c r="K23" s="1">
-        <v>9</v>
-      </c>
-      <c r="L23" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:12">
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -1784,22 +1966,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="1">
-        <v>2</v>
-      </c>
-      <c r="J24" s="1">
-        <v>6</v>
-      </c>
-      <c r="K24" s="1">
-        <v>9</v>
-      </c>
-      <c r="L24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1810,22 +1980,10 @@
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="1">
-        <v>2</v>
-      </c>
-      <c r="J25" s="1">
-        <v>6</v>
-      </c>
-      <c r="K25" s="1">
-        <v>9</v>
-      </c>
-      <c r="L25" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -1836,24 +1994,12 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G26" s="1">
-        <v>2</v>
-      </c>
-      <c r="J26" s="1">
-        <v>6</v>
-      </c>
-      <c r="K26" s="1">
-        <v>9</v>
-      </c>
-      <c r="L26" s="1">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:F3 E4 F4 E5:F5 O3:O5 C3:D5 G3:H5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
